--- a/Feuilles/Jamais ideal.xlsx
+++ b/Feuilles/Jamais ideal.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C72D48D9-CCFB-7440-9499-E57D1888A793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125606C4-BC4D-4F43-8087-D7D1508324A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="4160" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
+    <workbookView xWindow="15740" yWindow="1120" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>MES</t>
   </si>
@@ -80,23 +80,33 @@
     <t>COUPLET 4</t>
   </si>
   <si>
-    <t>REFRAIN 5</t>
-  </si>
-  <si>
     <t>Chœurs</t>
   </si>
   <si>
     <t>Choeurs ( bis)</t>
+  </si>
+  <si>
+    <t>LOOP</t>
+  </si>
+  <si>
+    <t>REFRAIN 4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -122,8 +132,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -458,10 +469,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B34C31-2D9C-7940-9F39-E67ACD52E89F}">
-  <dimension ref="A1:D224"/>
+  <dimension ref="A1:E224"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -474,8 +488,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -489,7 +506,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -500,7 +517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -511,7 +528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -522,7 +539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -533,7 +550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -544,7 +561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -555,7 +572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -566,7 +583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -577,7 +594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -588,7 +605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -599,7 +616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -610,7 +627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -621,7 +638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -632,7 +649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -643,7 +660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -654,7 +671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -668,7 +685,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -679,7 +696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -690,7 +707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -701,7 +718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -712,7 +729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -723,7 +740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -734,7 +751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -745,7 +762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -756,7 +773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -767,7 +784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -778,7 +795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -789,7 +806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -802,8 +819,11 @@
       <c r="D30" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -814,7 +834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -825,7 +845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -836,7 +856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -847,7 +867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -858,7 +878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -869,7 +889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -880,7 +900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -893,8 +913,11 @@
       <c r="D38" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -905,7 +928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -916,7 +939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -927,7 +950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -938,7 +961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -949,7 +972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -960,7 +983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -971,7 +994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -982,7 +1005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -993,7 +1016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1004,7 +1027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1015,7 +1038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1028,8 +1051,11 @@
       <c r="D50" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1039,8 +1065,9 @@
       <c r="C51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E51" s="1"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1050,8 +1077,9 @@
       <c r="C52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E52" s="1"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1061,8 +1089,9 @@
       <c r="C53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E53" s="1"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1072,8 +1101,9 @@
       <c r="C54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E54" s="1"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1083,8 +1113,9 @@
       <c r="C55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E55" s="1"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1094,8 +1125,9 @@
       <c r="C56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E56" s="1"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1105,8 +1137,9 @@
       <c r="C57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E57" s="1"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1119,8 +1152,11 @@
       <c r="D58" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1131,7 +1167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1142,7 +1178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1153,7 +1189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1164,7 +1200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1175,7 +1211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1186,7 +1222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1197,7 +1233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1208,7 +1244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1219,7 +1255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1232,8 +1268,11 @@
       <c r="D68" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1243,8 +1282,9 @@
       <c r="C69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E69" s="1"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1254,8 +1294,9 @@
       <c r="C70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E70" s="1"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1265,8 +1306,9 @@
       <c r="C71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E71" s="1"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1276,8 +1318,9 @@
       <c r="C72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E72" s="1"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1287,8 +1330,9 @@
       <c r="C73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E73" s="1"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -1298,8 +1342,9 @@
       <c r="C74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E74" s="1"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -1309,8 +1354,9 @@
       <c r="C75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E75" s="1"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -1320,8 +1366,11 @@
       <c r="C76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E76" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -1331,8 +1380,9 @@
       <c r="C77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E77" s="1"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -1342,8 +1392,9 @@
       <c r="C78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E78" s="1"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -1353,8 +1404,9 @@
       <c r="C79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E79" s="1"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -1367,8 +1419,11 @@
       <c r="D80" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E80" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -1378,8 +1433,9 @@
       <c r="C81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E81" s="1"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -1389,8 +1445,9 @@
       <c r="C82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E82" s="1"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -1400,8 +1457,9 @@
       <c r="C83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E83" s="1"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -1411,8 +1469,9 @@
       <c r="C84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E84" s="1"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -1422,8 +1481,9 @@
       <c r="C85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E85" s="1"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -1433,8 +1493,9 @@
       <c r="C86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E86" s="1"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -1444,8 +1505,9 @@
       <c r="C87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E87" s="1"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -1456,7 +1518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -1467,7 +1529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -1478,7 +1540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -1489,7 +1551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -1500,10 +1562,13 @@
         <v>0</v>
       </c>
       <c r="D92" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+      <c r="E92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -1514,7 +1579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -1525,7 +1590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -1536,7 +1601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
@@ -1547,7 +1612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -1558,7 +1623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -1569,7 +1634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -1580,7 +1645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>99</v>
       </c>
@@ -1591,10 +1656,13 @@
         <v>0</v>
       </c>
       <c r="D100" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>100</v>
       </c>
@@ -1605,7 +1673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>101</v>
       </c>
@@ -1616,7 +1684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>102</v>
       </c>
@@ -1627,7 +1695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>103</v>
       </c>
@@ -1638,7 +1706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>104</v>
       </c>
@@ -1649,7 +1717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>105</v>
       </c>
@@ -1660,7 +1728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>106</v>
       </c>
@@ -1671,7 +1739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>107</v>
       </c>
@@ -1681,8 +1749,11 @@
       <c r="C108">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>108</v>
       </c>
@@ -1693,7 +1764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>109</v>
       </c>
@@ -1704,7 +1775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>110</v>
       </c>
@@ -1715,7 +1786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>111</v>
       </c>
@@ -1726,7 +1797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>112</v>
       </c>
@@ -1737,7 +1808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>113</v>
       </c>
@@ -1748,7 +1819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>114</v>
       </c>
@@ -1759,7 +1830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>115</v>
       </c>
@@ -1770,10 +1841,13 @@
         <v>0</v>
       </c>
       <c r="D116" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+      <c r="E116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>116</v>
       </c>
@@ -1784,7 +1858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>117</v>
       </c>
@@ -1795,7 +1869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>118</v>
       </c>
@@ -1806,7 +1880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>119</v>
       </c>
@@ -1817,7 +1891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>120</v>
       </c>
@@ -1828,7 +1902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>121</v>
       </c>
@@ -1839,7 +1913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>122</v>
       </c>
@@ -1850,7 +1924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>123</v>
       </c>
@@ -1860,8 +1934,11 @@
       <c r="C124">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>124</v>
       </c>
@@ -1872,7 +1949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>125</v>
       </c>
@@ -1883,7 +1960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>126</v>
       </c>
@@ -1894,7 +1971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>127</v>
       </c>
@@ -1905,7 +1982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>128</v>
       </c>
@@ -1916,7 +1993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>129</v>
       </c>
@@ -1927,7 +2004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>130</v>
       </c>
@@ -1940,8 +2017,11 @@
       <c r="D131" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>131</v>
       </c>
@@ -1952,7 +2032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>132</v>
       </c>
@@ -1963,7 +2043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>133</v>
       </c>
@@ -1974,7 +2054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>134</v>
       </c>
@@ -1985,7 +2065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>135</v>
       </c>
@@ -1996,7 +2076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>136</v>
       </c>
@@ -2007,7 +2087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>137</v>
       </c>
@@ -2018,7 +2098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>138</v>
       </c>
@@ -2029,7 +2109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>139</v>
       </c>
@@ -2040,7 +2120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>140</v>
       </c>
@@ -2051,7 +2131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>141</v>
       </c>
@@ -2062,7 +2142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>142</v>
       </c>
@@ -2073,7 +2153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>143</v>
       </c>

--- a/Feuilles/Jamais ideal.xlsx
+++ b/Feuilles/Jamais ideal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125606C4-BC4D-4F43-8087-D7D1508324A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{774D8549-98DF-C047-839B-656087FC6DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15740" yWindow="1120" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
+    <workbookView xWindow="10360" yWindow="1120" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -2018,7 +2018,7 @@
         <v>9</v>
       </c>
       <c r="E131">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
